--- a/output_files/checklist.xlsx
+++ b/output_files/checklist.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,22 +538,22 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>27791827.5</v>
+        <v>24506402.5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>26133642.99</v>
+        <v>23153041.72</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>25190441.32</v>
+        <v>22576855.33</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>943202.88</v>
+        <v>576188.0699999999</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1405217.55</v>
+        <v>1146898.52</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>252964.97</v>
+        <v>206458.39</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
@@ -574,10 +574,10 @@
         <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>26133644.98</v>
+        <v>23153045.59</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-1.99</v>
+        <v>-3.87</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -589,68 +589,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>35884.17</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Return</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>-800</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>-759.97</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>-759.97</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-33.92</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>-6.11</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>-759.97</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0</v>
+        <v>15379.25</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,144 +647,168 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>26133642.99</v>
+        <v>23153041.72</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>25190441.32</v>
+        <v>22576855.33</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>943202.88</v>
+        <v>576188.0699999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-1.209999998216517</v>
+        <v>-1.679999999352731</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-759.97</v>
+        <v>23153041.72</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-759.97</v>
+        <v>22576855.33</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>576188.0699999999</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>26132883.02</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>25189681.35</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>943202.88</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>-1.209999998216517</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+        <v>-1.679999999352731</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2  Check list _Payout Calculation</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>direction_name</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>GMV</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>cust_shipping_reversal</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>partial_shipping_reversal</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>pf</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>product_gst</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>TDS</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Seller Payable</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>merchant_payable</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>direction_name</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>GMV</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Commission</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Tax</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>cust_shipping_reversal</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>partial_shipping_reversal</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>pf</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="inlineStr">
-        <is>
-          <t>product_gst</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>TDS</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>Seller Payable</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr">
-        <is>
-          <t>merchant_payable</t>
-        </is>
-      </c>
-      <c r="M11" s="1" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>24506402.5</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1146898.52</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>206458.39</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>23153045.59</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>23153041.72</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>3.870000001043081</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>payout</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>27791827.5</v>
+        <v>24506402.5</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1405217.55</v>
+        <v>1146898.52</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>252964.97</v>
+        <v>206458.39</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -866,176 +829,90 @@
         <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>26133644.98</v>
+        <v>23153045.59</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>26133642.99</v>
+        <v>23153041.72</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1.989999998360872</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Return</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>-800</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>-33.92</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>-6.11</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>-759.97</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>-759.97</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>27791027.5</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>1405183.63</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>252958.86</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>26132885.01</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>26132883.02</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>1.989999998360872</v>
+        <v>3.870000001043081</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3 Check list _File Wise Comparison</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3 Check list _File Wise Comparison</t>
-        </is>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>File name</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>pg_payable</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>cod_payable</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Compact revenue report</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>22576855.33</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>576188.0699999999</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>23153043.4</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>File name</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>pg_payable</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>cod_payable</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Merchant payout report</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>22576855.33</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>576188.0699999999</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>23153043.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Compact revenue report</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>25189681.35</v>
+        <v>0</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>943202.88</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>26132884.23</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Merchant payout report</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>25189681.35</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>943200.92</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>26132882.27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
